--- a/public/informes-templates/INFORME ARRANCADOR .xlsx
+++ b/public/informes-templates/INFORME ARRANCADOR .xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB68DE02-AEAF-4195-B83B-1310D5036FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D154FD2-BCD3-423A-8CAB-9ABC77BF445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
   <si>
     <t>INFORME DE SERVICIO</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>FECHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EQUIPO 1 </t>
   </si>
   <si>
     <t>DATOS DEL EQUIPO</t>
@@ -624,8 +621,8 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -633,11 +630,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -645,16 +666,43 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -666,20 +714,11 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -690,59 +729,17 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1018,7 +1015,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="24"/>
@@ -1048,15 +1045,15 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="38"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="28"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1076,12 +1073,12 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="60"/>
+      <c r="A3" s="29"/>
       <c r="B3" s="25"/>
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="61"/>
+      <c r="D3" s="32"/>
       <c r="E3" s="24"/>
       <c r="F3" s="24"/>
       <c r="G3" s="24"/>
@@ -1106,12 +1103,12 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47"/>
-      <c r="B4" s="41"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="61"/>
+      <c r="D4" s="32"/>
       <c r="E4" s="24"/>
       <c r="F4" s="24"/>
       <c r="G4" s="24"/>
@@ -1136,12 +1133,12 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47"/>
-      <c r="B5" s="41"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="31"/>
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="61"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="24"/>
       <c r="F5" s="24"/>
       <c r="G5" s="24"/>
@@ -1166,12 +1163,12 @@
       <c r="Z5" s="1"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47"/>
-      <c r="B6" s="41"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="31"/>
       <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="61"/>
+      <c r="D6" s="32"/>
       <c r="E6" s="24"/>
       <c r="F6" s="24"/>
       <c r="G6" s="24"/>
@@ -1196,12 +1193,12 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="47"/>
-      <c r="B7" s="41"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="31"/>
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="61"/>
+      <c r="D7" s="32"/>
       <c r="E7" s="24"/>
       <c r="F7" s="24"/>
       <c r="G7" s="24"/>
@@ -1226,12 +1223,12 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="47"/>
-      <c r="B8" s="41"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="31"/>
       <c r="C8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="62"/>
+      <c r="D8" s="33"/>
       <c r="E8" s="24"/>
       <c r="F8" s="24"/>
       <c r="G8" s="24"/>
@@ -1256,12 +1253,12 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="47"/>
-      <c r="B9" s="41"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="31"/>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="62"/>
+      <c r="D9" s="33"/>
       <c r="E9" s="24"/>
       <c r="F9" s="24"/>
       <c r="G9" s="24"/>
@@ -1286,12 +1283,12 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="41"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="31"/>
       <c r="C10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="61"/>
+      <c r="D10" s="32"/>
       <c r="E10" s="24"/>
       <c r="F10" s="24"/>
       <c r="G10" s="24"/>
@@ -1316,12 +1313,12 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="47"/>
-      <c r="B11" s="41"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="31"/>
       <c r="C11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="61"/>
+      <c r="D11" s="32"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
       <c r="G11" s="24"/>
@@ -1374,19 +1371,17 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="29"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="37"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -1406,26 +1401,26 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="47"/>
-      <c r="B14" s="41"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="31"/>
       <c r="C14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="F14" s="37"/>
+      <c r="G14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="29"/>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1446,12 +1441,12 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="47"/>
-      <c r="B15" s="41"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="31"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="29"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="37"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
@@ -1474,15 +1469,15 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="47"/>
-      <c r="B16" s="41"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="31"/>
       <c r="C16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="57"/>
+      <c r="E16" s="39"/>
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
@@ -1506,15 +1501,15 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="48"/>
-      <c r="B17" s="38"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="28"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="38"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="28"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1534,15 +1529,15 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
-        <v>20</v>
+      <c r="A18" s="42" t="s">
+        <v>19</v>
       </c>
       <c r="B18" s="24"/>
       <c r="C18" s="24"/>
       <c r="D18" s="24"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="26" t="s">
-        <v>21</v>
+      <c r="F18" s="42" t="s">
+        <v>20</v>
       </c>
       <c r="G18" s="24"/>
       <c r="H18" s="24"/>
@@ -1567,14 +1562,14 @@
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="13"/>
       <c r="D19" s="15"/>
-      <c r="E19" s="49"/>
+      <c r="E19" s="43"/>
       <c r="F19" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="13"/>
@@ -1599,14 +1594,14 @@
     </row>
     <row r="20" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="16"/>
       <c r="D20" s="18"/>
-      <c r="E20" s="50"/>
+      <c r="E20" s="44"/>
       <c r="F20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="16"/>
@@ -1631,14 +1626,14 @@
     </row>
     <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="16"/>
       <c r="D21" s="18"/>
-      <c r="E21" s="50"/>
+      <c r="E21" s="44"/>
       <c r="F21" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="16"/>
@@ -1663,14 +1658,14 @@
     </row>
     <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="16"/>
       <c r="D22" s="18"/>
-      <c r="E22" s="50"/>
+      <c r="E22" s="44"/>
       <c r="F22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="16"/>
@@ -1695,14 +1690,14 @@
     </row>
     <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="16"/>
       <c r="D23" s="18"/>
-      <c r="E23" s="50"/>
+      <c r="E23" s="44"/>
       <c r="F23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="16"/>
@@ -1727,14 +1722,14 @@
     </row>
     <row r="24" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="16"/>
       <c r="D24" s="18"/>
-      <c r="E24" s="50"/>
+      <c r="E24" s="44"/>
       <c r="F24" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="16"/>
@@ -1759,14 +1754,14 @@
     </row>
     <row r="25" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="16"/>
       <c r="D25" s="18"/>
-      <c r="E25" s="50"/>
+      <c r="E25" s="44"/>
       <c r="F25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="16"/>
@@ -1791,14 +1786,14 @@
     </row>
     <row r="26" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="16"/>
       <c r="D26" s="18"/>
-      <c r="E26" s="50"/>
+      <c r="E26" s="44"/>
       <c r="F26" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="16"/>
@@ -1823,14 +1818,14 @@
     </row>
     <row r="27" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="16"/>
       <c r="D27" s="18"/>
-      <c r="E27" s="50"/>
+      <c r="E27" s="44"/>
       <c r="F27" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="16"/>
@@ -1855,14 +1850,14 @@
     </row>
     <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="16"/>
       <c r="D28" s="18"/>
-      <c r="E28" s="50"/>
+      <c r="E28" s="44"/>
       <c r="F28" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="16"/>
@@ -1887,14 +1882,14 @@
     </row>
     <row r="29" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="16"/>
       <c r="D29" s="18"/>
-      <c r="E29" s="50"/>
+      <c r="E29" s="44"/>
       <c r="F29" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="16"/>
@@ -1919,14 +1914,14 @@
     </row>
     <row r="30" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="16"/>
       <c r="D30" s="18"/>
-      <c r="E30" s="50"/>
+      <c r="E30" s="44"/>
       <c r="F30" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="16"/>
@@ -1951,14 +1946,14 @@
     </row>
     <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="19"/>
       <c r="D31" s="21"/>
-      <c r="E31" s="50"/>
+      <c r="E31" s="44"/>
       <c r="F31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="19"/>
@@ -1982,21 +1977,21 @@
       <c r="Z31" s="1"/>
     </row>
     <row r="32" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="52" t="s">
+      <c r="A32" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="37"/>
+      <c r="C32" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="53" t="s">
+      <c r="D32" s="25"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" s="37"/>
+      <c r="H32" s="46" t="s">
         <v>36</v>
-      </c>
-      <c r="D32" s="25"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="G32" s="29"/>
-      <c r="H32" s="53" t="s">
-        <v>37</v>
       </c>
       <c r="I32" s="25"/>
       <c r="J32" s="1"/>
@@ -2018,15 +2013,15 @@
       <c r="Z32" s="1"/>
     </row>
     <row r="33" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="54"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="38"/>
+      <c r="A33" s="47"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="28"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -2046,17 +2041,17 @@
       <c r="Z33" s="1"/>
     </row>
     <row r="34" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="46" t="s">
-        <v>38</v>
+      <c r="A34" s="50" t="s">
+        <v>37</v>
       </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="29"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="37"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -2636,21 +2631,21 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="33" t="s">
+      <c r="A55" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="36"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="33" t="s">
+      <c r="E55" s="36"/>
+      <c r="F55" s="37"/>
+      <c r="G55" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="E55" s="28"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="H55" s="28"/>
-      <c r="I55" s="29"/>
+      <c r="H55" s="36"/>
+      <c r="I55" s="37"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -3230,21 +3225,21 @@
       <c r="Z75" s="1"/>
     </row>
     <row r="76" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="33" t="s">
+      <c r="A76" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="B76" s="36"/>
+      <c r="C76" s="37"/>
+      <c r="D76" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="B76" s="28"/>
-      <c r="C76" s="29"/>
-      <c r="D76" s="33" t="s">
+      <c r="E76" s="36"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="E76" s="28"/>
-      <c r="F76" s="29"/>
-      <c r="G76" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="H76" s="28"/>
-      <c r="I76" s="29"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="37"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
@@ -3824,21 +3819,21 @@
       <c r="Z96" s="1"/>
     </row>
     <row r="97" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="33" t="s">
+      <c r="A97" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="B97" s="36"/>
+      <c r="C97" s="37"/>
+      <c r="D97" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="B97" s="28"/>
-      <c r="C97" s="29"/>
-      <c r="D97" s="33" t="s">
+      <c r="E97" s="36"/>
+      <c r="F97" s="37"/>
+      <c r="G97" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="E97" s="28"/>
-      <c r="F97" s="29"/>
-      <c r="G97" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="H97" s="28"/>
-      <c r="I97" s="29"/>
+      <c r="H97" s="36"/>
+      <c r="I97" s="37"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
@@ -3858,15 +3853,15 @@
       <c r="Z97" s="1"/>
     </row>
     <row r="98" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="34"/>
-      <c r="B98" s="35"/>
-      <c r="C98" s="35"/>
-      <c r="D98" s="35"/>
-      <c r="E98" s="35"/>
-      <c r="F98" s="35"/>
-      <c r="G98" s="35"/>
-      <c r="H98" s="35"/>
-      <c r="I98" s="35"/>
+      <c r="A98" s="51"/>
+      <c r="B98" s="52"/>
+      <c r="C98" s="52"/>
+      <c r="D98" s="52"/>
+      <c r="E98" s="52"/>
+      <c r="F98" s="52"/>
+      <c r="G98" s="52"/>
+      <c r="H98" s="52"/>
+      <c r="I98" s="52"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
@@ -3886,19 +3881,19 @@
       <c r="Z98" s="1"/>
     </row>
     <row r="99" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="36" t="s">
+      <c r="A99" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="B99" s="27"/>
+      <c r="C99" s="28"/>
+      <c r="D99" s="54"/>
+      <c r="E99" s="52"/>
+      <c r="F99" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="B99" s="37"/>
-      <c r="C99" s="38"/>
-      <c r="D99" s="39"/>
-      <c r="E99" s="35"/>
-      <c r="F99" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="G99" s="35"/>
-      <c r="H99" s="35"/>
-      <c r="I99" s="41"/>
+      <c r="G99" s="52"/>
+      <c r="H99" s="52"/>
+      <c r="I99" s="31"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
@@ -3919,24 +3914,24 @@
     </row>
     <row r="100" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B100" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B100" s="10" t="s">
+      <c r="C100" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C100" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D100" s="35"/>
-      <c r="E100" s="35"/>
+      <c r="D100" s="52"/>
+      <c r="E100" s="52"/>
       <c r="F100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G100" s="32" t="s">
-        <v>52</v>
+      <c r="G100" s="35" t="s">
+        <v>51</v>
       </c>
-      <c r="H100" s="28"/>
-      <c r="I100" s="29"/>
+      <c r="H100" s="36"/>
+      <c r="I100" s="37"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
       <c r="L100" s="1"/>
@@ -3957,16 +3952,16 @@
     </row>
     <row r="101" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
-      <c r="D101" s="35"/>
-      <c r="E101" s="35"/>
+      <c r="D101" s="52"/>
+      <c r="E101" s="52"/>
       <c r="F101" s="6"/>
-      <c r="G101" s="42"/>
-      <c r="H101" s="28"/>
-      <c r="I101" s="29"/>
+      <c r="G101" s="56"/>
+      <c r="H101" s="36"/>
+      <c r="I101" s="37"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -3987,16 +3982,16 @@
     </row>
     <row r="102" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
-      <c r="D102" s="35"/>
-      <c r="E102" s="35"/>
+      <c r="D102" s="52"/>
+      <c r="E102" s="52"/>
       <c r="F102" s="6"/>
-      <c r="G102" s="42"/>
-      <c r="H102" s="28"/>
-      <c r="I102" s="29"/>
+      <c r="G102" s="56"/>
+      <c r="H102" s="36"/>
+      <c r="I102" s="37"/>
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
@@ -4017,16 +4012,16 @@
     </row>
     <row r="103" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
-      <c r="D103" s="35"/>
-      <c r="E103" s="35"/>
+      <c r="D103" s="52"/>
+      <c r="E103" s="52"/>
       <c r="F103" s="6"/>
-      <c r="G103" s="42"/>
-      <c r="H103" s="28"/>
-      <c r="I103" s="29"/>
+      <c r="G103" s="56"/>
+      <c r="H103" s="36"/>
+      <c r="I103" s="37"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -4047,16 +4042,16 @@
     </row>
     <row r="104" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
-      <c r="B104" s="43"/>
-      <c r="C104" s="29"/>
-      <c r="D104" s="35"/>
-      <c r="E104" s="35"/>
+      <c r="B104" s="57"/>
+      <c r="C104" s="37"/>
+      <c r="D104" s="52"/>
+      <c r="E104" s="52"/>
       <c r="F104" s="6"/>
-      <c r="G104" s="42"/>
-      <c r="H104" s="28"/>
-      <c r="I104" s="29"/>
+      <c r="G104" s="56"/>
+      <c r="H104" s="36"/>
+      <c r="I104" s="37"/>
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
@@ -4076,15 +4071,15 @@
       <c r="Z104" s="1"/>
     </row>
     <row r="105" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="44"/>
+      <c r="A105" s="58"/>
       <c r="B105" s="24"/>
       <c r="C105" s="24"/>
-      <c r="D105" s="35"/>
-      <c r="E105" s="35"/>
+      <c r="D105" s="52"/>
+      <c r="E105" s="52"/>
       <c r="F105" s="6"/>
-      <c r="G105" s="42"/>
-      <c r="H105" s="28"/>
-      <c r="I105" s="29"/>
+      <c r="G105" s="56"/>
+      <c r="H105" s="36"/>
+      <c r="I105" s="37"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -4104,8 +4099,8 @@
       <c r="Z105" s="1"/>
     </row>
     <row r="106" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="31" t="s">
-        <v>57</v>
+      <c r="A106" s="59" t="s">
+        <v>56</v>
       </c>
       <c r="B106" s="24"/>
       <c r="C106" s="24"/>
@@ -4135,21 +4130,21 @@
     </row>
     <row r="107" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B107" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="B107" s="32" t="s">
+      <c r="C107" s="36"/>
+      <c r="D107" s="36"/>
+      <c r="E107" s="36"/>
+      <c r="F107" s="36"/>
+      <c r="G107" s="36"/>
+      <c r="H107" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C107" s="28"/>
-      <c r="D107" s="28"/>
-      <c r="E107" s="28"/>
-      <c r="F107" s="28"/>
-      <c r="G107" s="28"/>
-      <c r="H107" s="3" t="s">
+      <c r="I107" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="I107" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
@@ -4173,14 +4168,14 @@
       <c r="A108" s="12">
         <v>1</v>
       </c>
-      <c r="B108" s="30" t="s">
-        <v>62</v>
+      <c r="B108" s="60" t="s">
+        <v>61</v>
       </c>
-      <c r="C108" s="28"/>
-      <c r="D108" s="28"/>
-      <c r="E108" s="28"/>
-      <c r="F108" s="28"/>
-      <c r="G108" s="29"/>
+      <c r="C108" s="36"/>
+      <c r="D108" s="36"/>
+      <c r="E108" s="36"/>
+      <c r="F108" s="36"/>
+      <c r="G108" s="37"/>
       <c r="H108" s="6"/>
       <c r="I108" s="6"/>
       <c r="J108" s="1"/>
@@ -4205,14 +4200,14 @@
       <c r="A109" s="12">
         <v>2</v>
       </c>
-      <c r="B109" s="30" t="s">
-        <v>63</v>
+      <c r="B109" s="60" t="s">
+        <v>62</v>
       </c>
-      <c r="C109" s="28"/>
-      <c r="D109" s="28"/>
-      <c r="E109" s="28"/>
-      <c r="F109" s="28"/>
-      <c r="G109" s="29"/>
+      <c r="C109" s="36"/>
+      <c r="D109" s="36"/>
+      <c r="E109" s="36"/>
+      <c r="F109" s="36"/>
+      <c r="G109" s="37"/>
       <c r="H109" s="6"/>
       <c r="I109" s="6"/>
       <c r="J109" s="1"/>
@@ -4237,14 +4232,14 @@
       <c r="A110" s="12">
         <v>3</v>
       </c>
-      <c r="B110" s="30" t="s">
-        <v>64</v>
+      <c r="B110" s="60" t="s">
+        <v>63</v>
       </c>
-      <c r="C110" s="28"/>
-      <c r="D110" s="28"/>
-      <c r="E110" s="28"/>
-      <c r="F110" s="28"/>
-      <c r="G110" s="29"/>
+      <c r="C110" s="36"/>
+      <c r="D110" s="36"/>
+      <c r="E110" s="36"/>
+      <c r="F110" s="36"/>
+      <c r="G110" s="37"/>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
       <c r="J110" s="1"/>
@@ -4269,14 +4264,14 @@
       <c r="A111" s="12">
         <v>4</v>
       </c>
-      <c r="B111" s="30" t="s">
-        <v>65</v>
+      <c r="B111" s="60" t="s">
+        <v>64</v>
       </c>
-      <c r="C111" s="28"/>
-      <c r="D111" s="28"/>
-      <c r="E111" s="28"/>
-      <c r="F111" s="28"/>
-      <c r="G111" s="29"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+      <c r="G111" s="37"/>
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
       <c r="J111" s="1"/>
@@ -4301,14 +4296,14 @@
       <c r="A112" s="12">
         <v>5</v>
       </c>
-      <c r="B112" s="30" t="s">
-        <v>66</v>
+      <c r="B112" s="60" t="s">
+        <v>65</v>
       </c>
-      <c r="C112" s="28"/>
-      <c r="D112" s="28"/>
-      <c r="E112" s="28"/>
-      <c r="F112" s="28"/>
-      <c r="G112" s="29"/>
+      <c r="C112" s="36"/>
+      <c r="D112" s="36"/>
+      <c r="E112" s="36"/>
+      <c r="F112" s="36"/>
+      <c r="G112" s="37"/>
       <c r="H112" s="6"/>
       <c r="I112" s="6"/>
       <c r="J112" s="1"/>
@@ -4333,14 +4328,14 @@
       <c r="A113" s="12">
         <v>6</v>
       </c>
-      <c r="B113" s="30" t="s">
-        <v>67</v>
+      <c r="B113" s="60" t="s">
+        <v>66</v>
       </c>
-      <c r="C113" s="28"/>
-      <c r="D113" s="28"/>
-      <c r="E113" s="28"/>
-      <c r="F113" s="28"/>
-      <c r="G113" s="29"/>
+      <c r="C113" s="36"/>
+      <c r="D113" s="36"/>
+      <c r="E113" s="36"/>
+      <c r="F113" s="36"/>
+      <c r="G113" s="37"/>
       <c r="H113" s="6"/>
       <c r="I113" s="6"/>
       <c r="J113" s="1"/>
@@ -4365,14 +4360,14 @@
       <c r="A114" s="12">
         <v>7</v>
       </c>
-      <c r="B114" s="30" t="s">
-        <v>68</v>
+      <c r="B114" s="60" t="s">
+        <v>67</v>
       </c>
-      <c r="C114" s="28"/>
-      <c r="D114" s="28"/>
-      <c r="E114" s="28"/>
-      <c r="F114" s="28"/>
-      <c r="G114" s="29"/>
+      <c r="C114" s="36"/>
+      <c r="D114" s="36"/>
+      <c r="E114" s="36"/>
+      <c r="F114" s="36"/>
+      <c r="G114" s="37"/>
       <c r="H114" s="6"/>
       <c r="I114" s="6"/>
       <c r="J114" s="1"/>
@@ -4397,14 +4392,14 @@
       <c r="A115" s="12">
         <v>8</v>
       </c>
-      <c r="B115" s="30" t="s">
-        <v>69</v>
+      <c r="B115" s="60" t="s">
+        <v>68</v>
       </c>
-      <c r="C115" s="28"/>
-      <c r="D115" s="28"/>
-      <c r="E115" s="28"/>
-      <c r="F115" s="28"/>
-      <c r="G115" s="29"/>
+      <c r="C115" s="36"/>
+      <c r="D115" s="36"/>
+      <c r="E115" s="36"/>
+      <c r="F115" s="36"/>
+      <c r="G115" s="37"/>
       <c r="H115" s="6"/>
       <c r="I115" s="6"/>
       <c r="J115" s="1"/>
@@ -4429,14 +4424,14 @@
       <c r="A116" s="12">
         <v>9</v>
       </c>
-      <c r="B116" s="30" t="s">
-        <v>70</v>
+      <c r="B116" s="60" t="s">
+        <v>69</v>
       </c>
-      <c r="C116" s="28"/>
-      <c r="D116" s="28"/>
-      <c r="E116" s="28"/>
-      <c r="F116" s="28"/>
-      <c r="G116" s="29"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+      <c r="G116" s="37"/>
       <c r="H116" s="6"/>
       <c r="I116" s="6"/>
       <c r="J116" s="1"/>
@@ -4461,14 +4456,14 @@
       <c r="A117" s="12">
         <v>10</v>
       </c>
-      <c r="B117" s="30" t="s">
-        <v>71</v>
+      <c r="B117" s="60" t="s">
+        <v>70</v>
       </c>
-      <c r="C117" s="28"/>
-      <c r="D117" s="28"/>
-      <c r="E117" s="28"/>
-      <c r="F117" s="28"/>
-      <c r="G117" s="29"/>
+      <c r="C117" s="36"/>
+      <c r="D117" s="36"/>
+      <c r="E117" s="36"/>
+      <c r="F117" s="36"/>
+      <c r="G117" s="37"/>
       <c r="H117" s="6"/>
       <c r="I117" s="6"/>
       <c r="J117" s="1"/>
@@ -4493,14 +4488,14 @@
       <c r="A118" s="12">
         <v>11</v>
       </c>
-      <c r="B118" s="30" t="s">
-        <v>72</v>
+      <c r="B118" s="60" t="s">
+        <v>71</v>
       </c>
-      <c r="C118" s="28"/>
-      <c r="D118" s="28"/>
-      <c r="E118" s="28"/>
-      <c r="F118" s="28"/>
-      <c r="G118" s="29"/>
+      <c r="C118" s="36"/>
+      <c r="D118" s="36"/>
+      <c r="E118" s="36"/>
+      <c r="F118" s="36"/>
+      <c r="G118" s="37"/>
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
       <c r="J118" s="1"/>
@@ -4525,14 +4520,14 @@
       <c r="A119" s="12">
         <v>12</v>
       </c>
-      <c r="B119" s="30" t="s">
-        <v>73</v>
+      <c r="B119" s="60" t="s">
+        <v>72</v>
       </c>
-      <c r="C119" s="28"/>
-      <c r="D119" s="28"/>
-      <c r="E119" s="28"/>
-      <c r="F119" s="28"/>
-      <c r="G119" s="29"/>
+      <c r="C119" s="36"/>
+      <c r="D119" s="36"/>
+      <c r="E119" s="36"/>
+      <c r="F119" s="36"/>
+      <c r="G119" s="37"/>
       <c r="H119" s="6"/>
       <c r="I119" s="6"/>
       <c r="J119" s="1"/>
@@ -4557,14 +4552,14 @@
       <c r="A120" s="12">
         <v>13</v>
       </c>
-      <c r="B120" s="30" t="s">
-        <v>74</v>
+      <c r="B120" s="60" t="s">
+        <v>73</v>
       </c>
-      <c r="C120" s="28"/>
-      <c r="D120" s="28"/>
-      <c r="E120" s="28"/>
-      <c r="F120" s="28"/>
-      <c r="G120" s="29"/>
+      <c r="C120" s="36"/>
+      <c r="D120" s="36"/>
+      <c r="E120" s="36"/>
+      <c r="F120" s="36"/>
+      <c r="G120" s="37"/>
       <c r="H120" s="6"/>
       <c r="I120" s="6"/>
       <c r="J120" s="1"/>
@@ -4586,8 +4581,8 @@
       <c r="Z120" s="1"/>
     </row>
     <row r="121" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="26" t="s">
-        <v>56</v>
+      <c r="A121" s="42" t="s">
+        <v>55</v>
       </c>
       <c r="B121" s="24"/>
       <c r="C121" s="24"/>
@@ -4616,7 +4611,7 @@
       <c r="Z121" s="1"/>
     </row>
     <row r="122" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="23"/>
+      <c r="A122" s="61"/>
       <c r="B122" s="24"/>
       <c r="C122" s="24"/>
       <c r="D122" s="24"/>
@@ -4644,8 +4639,8 @@
       <c r="Z122" s="1"/>
     </row>
     <row r="123" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="26" t="s">
-        <v>75</v>
+      <c r="A123" s="42" t="s">
+        <v>74</v>
       </c>
       <c r="B123" s="24"/>
       <c r="C123" s="24"/>
@@ -4674,7 +4669,7 @@
       <c r="Z123" s="1"/>
     </row>
     <row r="124" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="23"/>
+      <c r="A124" s="61"/>
       <c r="B124" s="24"/>
       <c r="C124" s="24"/>
       <c r="D124" s="24"/>
@@ -4702,7 +4697,7 @@
       <c r="Z124" s="1"/>
     </row>
     <row r="125" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="23"/>
+      <c r="A125" s="61"/>
       <c r="B125" s="24"/>
       <c r="C125" s="24"/>
       <c r="D125" s="24"/>
@@ -4730,7 +4725,7 @@
       <c r="Z125" s="1"/>
     </row>
     <row r="126" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="23"/>
+      <c r="A126" s="61"/>
       <c r="B126" s="24"/>
       <c r="C126" s="24"/>
       <c r="D126" s="24"/>
@@ -4758,8 +4753,8 @@
       <c r="Z126" s="1"/>
     </row>
     <row r="127" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="26" t="s">
-        <v>76</v>
+      <c r="A127" s="42" t="s">
+        <v>75</v>
       </c>
       <c r="B127" s="24"/>
       <c r="C127" s="24"/>
@@ -4788,15 +4783,15 @@
       <c r="Z127" s="1"/>
     </row>
     <row r="128" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="27"/>
-      <c r="B128" s="28"/>
-      <c r="C128" s="28"/>
-      <c r="D128" s="28"/>
-      <c r="E128" s="28"/>
-      <c r="F128" s="28"/>
-      <c r="G128" s="28"/>
-      <c r="H128" s="28"/>
-      <c r="I128" s="29"/>
+      <c r="A128" s="62"/>
+      <c r="B128" s="36"/>
+      <c r="C128" s="36"/>
+      <c r="D128" s="36"/>
+      <c r="E128" s="36"/>
+      <c r="F128" s="36"/>
+      <c r="G128" s="36"/>
+      <c r="H128" s="36"/>
+      <c r="I128" s="37"/>
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
@@ -4816,15 +4811,15 @@
       <c r="Z128" s="1"/>
     </row>
     <row r="129" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="27"/>
-      <c r="B129" s="28"/>
-      <c r="C129" s="28"/>
-      <c r="D129" s="28"/>
-      <c r="E129" s="28"/>
-      <c r="F129" s="28"/>
-      <c r="G129" s="28"/>
-      <c r="H129" s="28"/>
-      <c r="I129" s="29"/>
+      <c r="A129" s="62"/>
+      <c r="B129" s="36"/>
+      <c r="C129" s="36"/>
+      <c r="D129" s="36"/>
+      <c r="E129" s="36"/>
+      <c r="F129" s="36"/>
+      <c r="G129" s="36"/>
+      <c r="H129" s="36"/>
+      <c r="I129" s="37"/>
       <c r="J129" s="1"/>
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
@@ -10949,39 +10944,30 @@
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="A1:I2"/>
-    <mergeCell ref="A3:B11"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="A13:B17"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:I17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="E19:E33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D33"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I33"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="G76:I76"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="A126:I126"/>
+    <mergeCell ref="A127:I127"/>
+    <mergeCell ref="A128:I128"/>
+    <mergeCell ref="A129:I129"/>
+    <mergeCell ref="A121:I121"/>
+    <mergeCell ref="A122:I122"/>
+    <mergeCell ref="A123:I123"/>
+    <mergeCell ref="A124:I124"/>
+    <mergeCell ref="A125:I125"/>
+    <mergeCell ref="B116:G116"/>
+    <mergeCell ref="B117:G117"/>
+    <mergeCell ref="B118:G118"/>
+    <mergeCell ref="B119:G119"/>
+    <mergeCell ref="B120:G120"/>
+    <mergeCell ref="B111:G111"/>
+    <mergeCell ref="B112:G112"/>
+    <mergeCell ref="B113:G113"/>
+    <mergeCell ref="B114:G114"/>
+    <mergeCell ref="B115:G115"/>
+    <mergeCell ref="A106:I106"/>
+    <mergeCell ref="B107:G107"/>
+    <mergeCell ref="B108:G108"/>
+    <mergeCell ref="B109:G109"/>
+    <mergeCell ref="B110:G110"/>
     <mergeCell ref="A97:C97"/>
     <mergeCell ref="D97:F97"/>
     <mergeCell ref="G97:I97"/>
@@ -10997,30 +10983,39 @@
     <mergeCell ref="G104:I104"/>
     <mergeCell ref="A105:C105"/>
     <mergeCell ref="G105:I105"/>
-    <mergeCell ref="A106:I106"/>
-    <mergeCell ref="B107:G107"/>
-    <mergeCell ref="B108:G108"/>
-    <mergeCell ref="B109:G109"/>
-    <mergeCell ref="B110:G110"/>
-    <mergeCell ref="B111:G111"/>
-    <mergeCell ref="B112:G112"/>
-    <mergeCell ref="B113:G113"/>
-    <mergeCell ref="B114:G114"/>
-    <mergeCell ref="B115:G115"/>
-    <mergeCell ref="B116:G116"/>
-    <mergeCell ref="B117:G117"/>
-    <mergeCell ref="B118:G118"/>
-    <mergeCell ref="B119:G119"/>
-    <mergeCell ref="B120:G120"/>
-    <mergeCell ref="A126:I126"/>
-    <mergeCell ref="A127:I127"/>
-    <mergeCell ref="A128:I128"/>
-    <mergeCell ref="A129:I129"/>
-    <mergeCell ref="A121:I121"/>
-    <mergeCell ref="A122:I122"/>
-    <mergeCell ref="A123:I123"/>
-    <mergeCell ref="A124:I124"/>
-    <mergeCell ref="A125:I125"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="G76:I76"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="E19:E33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D33"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H32:I33"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A13:B17"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:I17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="A3:B11"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/public/informes-templates/INFORME ARRANCADOR .xlsx
+++ b/public/informes-templates/INFORME ARRANCADOR .xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D154FD2-BCD3-423A-8CAB-9ABC77BF445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D288EA5F-9A4A-4A89-A662-AD7E929DD036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,36 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
-  <si>
-    <t>INFORME DE SERVICIO</t>
-  </si>
-  <si>
-    <t>EMPRESA / CLIENTE</t>
-  </si>
-  <si>
-    <t>CONTACTO</t>
-  </si>
-  <si>
-    <t>ORDEN DE COMPRA</t>
-  </si>
-  <si>
-    <t>COT</t>
-  </si>
-  <si>
-    <t>LINEA / AREA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="68">
   <si>
     <t xml:space="preserve">DESCRIPCION </t>
   </si>
   <si>
-    <t>TIPO</t>
-  </si>
-  <si>
     <t>CANTIDAD</t>
-  </si>
-  <si>
-    <t>FECHA</t>
   </si>
   <si>
     <t>DATOS DEL EQUIPO</t>
@@ -249,7 +225,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,16 +239,19 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -280,11 +259,13 @@
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -292,25 +273,14 @@
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -318,6 +288,7 @@
       <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -325,11 +296,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -338,15 +311,17 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -369,6 +344,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -553,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -576,7 +557,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -585,41 +566,11 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -639,29 +590,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -669,14 +605,62 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -690,56 +674,89 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -756,55 +773,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1008,24 +976,24 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z347"/>
+  <dimension ref="A1:Z339"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="9" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="25"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="15"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -1045,15 +1013,15 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="28"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="18"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1073,17 +1041,15 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="25"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="20"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1103,17 +1069,15 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="25"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1133,17 +1097,17 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
+      <c r="A5" s="26" t="s">
+        <v>2</v>
       </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="25"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="28"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1163,17 +1127,27 @@
       <c r="Z5" s="1"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="32"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="25"/>
+      <c r="E6" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="22"/>
+      <c r="G6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1193,17 +1167,15 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="25"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1223,17 +1195,19 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
+      <c r="A8" s="3" t="s">
+        <v>9</v>
       </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="25"/>
+      <c r="B8" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="37"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="39"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1253,17 +1227,15 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="25"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="42"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -1283,17 +1255,19 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
+      <c r="A10" s="43" t="s">
+        <v>11</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="25"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -1313,17 +1287,19 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="3" t="s">
-        <v>9</v>
+      <c r="A11" s="2" t="s">
+        <v>13</v>
       </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="25"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="67"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -1343,15 +1319,19 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="70"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -1371,17 +1351,19 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="35" t="s">
-        <v>10</v>
+      <c r="A13" s="2" t="s">
+        <v>15</v>
       </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="37"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="70"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -1401,27 +1383,19 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="37"/>
-      <c r="G14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="70"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -1441,15 +1415,19 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="70"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -1469,19 +1447,19 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="30"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="40" t="s">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="39"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="25"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="70"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -1501,15 +1479,19 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="28"/>
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="70"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1529,19 +1511,19 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="42" t="s">
+      <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="70"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -1564,16 +1546,16 @@
       <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="43"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="45"/>
       <c r="F19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="15"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="70"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -1596,16 +1578,16 @@
       <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="44"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="45"/>
       <c r="F20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="18"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="70"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -1628,16 +1610,16 @@
       <c r="A21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="44"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="45"/>
       <c r="F21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="18"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="70"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -1661,15 +1643,15 @@
         <v>24</v>
       </c>
       <c r="B22" s="6"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="44"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="45"/>
       <c r="F22" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G22" s="6"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="18"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="70"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -1692,16 +1674,16 @@
       <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="44"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="45"/>
       <c r="F23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="18"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="73"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -1721,19 +1703,23 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="2" t="s">
+      <c r="B24" s="22"/>
+      <c r="C24" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="15"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="18"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="15"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1753,17 +1739,13 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="6"/>
+      <c r="A25" s="47"/>
+      <c r="B25" s="18"/>
       <c r="C25" s="16"/>
       <c r="D25" s="18"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" s="6"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="18"/>
       <c r="H25" s="16"/>
       <c r="I25" s="18"/>
       <c r="J25" s="1"/>
@@ -1785,19 +1767,17 @@
       <c r="Z25" s="1"/>
     </row>
     <row r="26" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>28</v>
+      <c r="A26" s="51" t="s">
+        <v>29</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="18"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="22"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -1817,19 +1797,15 @@
       <c r="Z26" s="1"/>
     </row>
     <row r="27" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="18"/>
+      <c r="A27" s="65"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="67"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1849,19 +1825,15 @@
       <c r="Z27" s="1"/>
     </row>
     <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="18"/>
+      <c r="A28" s="68"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="70"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -1881,19 +1853,15 @@
       <c r="Z28" s="1"/>
     </row>
     <row r="29" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="18"/>
+      <c r="A29" s="68"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="69"/>
+      <c r="I29" s="70"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -1913,19 +1881,15 @@
       <c r="Z29" s="1"/>
     </row>
     <row r="30" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" s="6"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="18"/>
+      <c r="A30" s="68"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="70"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="68"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="70"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -1944,20 +1908,16 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="21"/>
+    <row r="31" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="68"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="70"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="68"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="70"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -1976,24 +1936,16 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="37"/>
-      <c r="C32" s="46" t="s">
-        <v>35</v>
-      </c>
-      <c r="D32" s="25"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="G32" s="37"/>
-      <c r="H32" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="I32" s="25"/>
+    <row r="32" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="68"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="70"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="68"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="70"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -2012,16 +1964,16 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="47"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="28"/>
+    <row r="33" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="68"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="68"/>
+      <c r="H33" s="69"/>
+      <c r="I33" s="70"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -2040,18 +1992,16 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="37"/>
+    <row r="34" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="68"/>
+      <c r="B34" s="69"/>
+      <c r="C34" s="70"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="68"/>
+      <c r="H34" s="69"/>
+      <c r="I34" s="70"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -2070,16 +2020,16 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15"/>
+    <row r="35" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="68"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="70"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="68"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="70"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -2098,16 +2048,16 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="18"/>
+    <row r="36" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="68"/>
+      <c r="B36" s="69"/>
+      <c r="C36" s="70"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="68"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="70"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -2126,16 +2076,16 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="16"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="18"/>
+    <row r="37" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="68"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="70"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="68"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="70"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -2154,16 +2104,16 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="16"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="18"/>
+    <row r="38" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="68"/>
+      <c r="B38" s="69"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="69"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="69"/>
+      <c r="I38" s="70"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -2183,15 +2133,15 @@
       <c r="Z38" s="1"/>
     </row>
     <row r="39" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="16"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="18"/>
+      <c r="A39" s="68"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="69"/>
+      <c r="I39" s="70"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -2211,15 +2161,15 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="16"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="18"/>
+      <c r="A40" s="68"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="69"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="68"/>
+      <c r="H40" s="69"/>
+      <c r="I40" s="70"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -2239,15 +2189,15 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="16"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="18"/>
+      <c r="A41" s="68"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="70"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -2267,15 +2217,15 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="16"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="18"/>
+      <c r="A42" s="68"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="69"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="68"/>
+      <c r="H42" s="69"/>
+      <c r="I42" s="70"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -2295,15 +2245,15 @@
       <c r="Z42" s="1"/>
     </row>
     <row r="43" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="16"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="18"/>
+      <c r="A43" s="68"/>
+      <c r="B43" s="69"/>
+      <c r="C43" s="70"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="69"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="68"/>
+      <c r="H43" s="69"/>
+      <c r="I43" s="70"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -2323,15 +2273,15 @@
       <c r="Z43" s="1"/>
     </row>
     <row r="44" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="16"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="18"/>
+      <c r="A44" s="68"/>
+      <c r="B44" s="69"/>
+      <c r="C44" s="70"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="68"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="70"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -2351,15 +2301,15 @@
       <c r="Z44" s="1"/>
     </row>
     <row r="45" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="16"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="18"/>
+      <c r="A45" s="68"/>
+      <c r="B45" s="69"/>
+      <c r="C45" s="70"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="68"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="70"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -2379,15 +2329,15 @@
       <c r="Z45" s="1"/>
     </row>
     <row r="46" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="16"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="18"/>
+      <c r="A46" s="68"/>
+      <c r="B46" s="69"/>
+      <c r="C46" s="70"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="73"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="72"/>
+      <c r="I46" s="73"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -2407,15 +2357,21 @@
       <c r="Z46" s="1"/>
     </row>
     <row r="47" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="16"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="16"/>
-      <c r="H47" s="17"/>
-      <c r="I47" s="18"/>
+      <c r="A47" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" s="49"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47" s="49"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="H47" s="49"/>
+      <c r="I47" s="22"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -2435,15 +2391,15 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="16"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="18"/>
+      <c r="A48" s="65"/>
+      <c r="B48" s="66"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="67"/>
+      <c r="G48" s="65"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="67"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -2463,15 +2419,15 @@
       <c r="Z48" s="1"/>
     </row>
     <row r="49" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="16"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="18"/>
+      <c r="A49" s="68"/>
+      <c r="B49" s="69"/>
+      <c r="C49" s="70"/>
+      <c r="D49" s="68"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="68"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="70"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -2491,15 +2447,15 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="16"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="17"/>
-      <c r="I50" s="18"/>
+      <c r="A50" s="68"/>
+      <c r="B50" s="69"/>
+      <c r="C50" s="70"/>
+      <c r="D50" s="68"/>
+      <c r="E50" s="69"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="68"/>
+      <c r="H50" s="69"/>
+      <c r="I50" s="70"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -2519,15 +2475,15 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="16"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="16"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="18"/>
+      <c r="A51" s="68"/>
+      <c r="B51" s="69"/>
+      <c r="C51" s="70"/>
+      <c r="D51" s="68"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="70"/>
+      <c r="G51" s="68"/>
+      <c r="H51" s="69"/>
+      <c r="I51" s="70"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -2547,15 +2503,15 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="16"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="18"/>
+      <c r="A52" s="68"/>
+      <c r="B52" s="69"/>
+      <c r="C52" s="70"/>
+      <c r="D52" s="68"/>
+      <c r="E52" s="69"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="68"/>
+      <c r="H52" s="69"/>
+      <c r="I52" s="70"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -2575,15 +2531,15 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="16"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="16"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="18"/>
+      <c r="A53" s="68"/>
+      <c r="B53" s="69"/>
+      <c r="C53" s="70"/>
+      <c r="D53" s="68"/>
+      <c r="E53" s="69"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="68"/>
+      <c r="H53" s="69"/>
+      <c r="I53" s="70"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -2603,15 +2559,15 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="16"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="21"/>
+      <c r="A54" s="68"/>
+      <c r="B54" s="69"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="68"/>
+      <c r="E54" s="69"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="68"/>
+      <c r="H54" s="69"/>
+      <c r="I54" s="70"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -2631,21 +2587,15 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="36"/>
-      <c r="C55" s="37"/>
-      <c r="D55" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="E55" s="36"/>
-      <c r="F55" s="37"/>
-      <c r="G55" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="H55" s="36"/>
-      <c r="I55" s="37"/>
+      <c r="A55" s="68"/>
+      <c r="B55" s="69"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="68"/>
+      <c r="E55" s="69"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="68"/>
+      <c r="H55" s="69"/>
+      <c r="I55" s="70"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -2665,15 +2615,15 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15"/>
+      <c r="A56" s="68"/>
+      <c r="B56" s="69"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="68"/>
+      <c r="E56" s="69"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="68"/>
+      <c r="H56" s="69"/>
+      <c r="I56" s="70"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -2693,15 +2643,15 @@
       <c r="Z56" s="1"/>
     </row>
     <row r="57" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="16"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="16"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="18"/>
+      <c r="A57" s="68"/>
+      <c r="B57" s="69"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="73"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="72"/>
+      <c r="I57" s="73"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -2721,15 +2671,15 @@
       <c r="Z57" s="1"/>
     </row>
     <row r="58" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="16"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="18"/>
+      <c r="A58" s="68"/>
+      <c r="B58" s="69"/>
+      <c r="C58" s="70"/>
+      <c r="D58" s="65"/>
+      <c r="E58" s="66"/>
+      <c r="F58" s="67"/>
+      <c r="G58" s="65"/>
+      <c r="H58" s="66"/>
+      <c r="I58" s="67"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -2749,15 +2699,15 @@
       <c r="Z58" s="1"/>
     </row>
     <row r="59" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="16"/>
-      <c r="B59" s="17"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="16"/>
-      <c r="H59" s="17"/>
-      <c r="I59" s="18"/>
+      <c r="A59" s="68"/>
+      <c r="B59" s="69"/>
+      <c r="C59" s="70"/>
+      <c r="D59" s="68"/>
+      <c r="E59" s="69"/>
+      <c r="F59" s="70"/>
+      <c r="G59" s="68"/>
+      <c r="H59" s="69"/>
+      <c r="I59" s="70"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -2777,15 +2727,15 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="16"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="16"/>
-      <c r="H60" s="17"/>
-      <c r="I60" s="18"/>
+      <c r="A60" s="68"/>
+      <c r="B60" s="69"/>
+      <c r="C60" s="70"/>
+      <c r="D60" s="68"/>
+      <c r="E60" s="69"/>
+      <c r="F60" s="70"/>
+      <c r="G60" s="68"/>
+      <c r="H60" s="69"/>
+      <c r="I60" s="70"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -2805,15 +2755,15 @@
       <c r="Z60" s="1"/>
     </row>
     <row r="61" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="16"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="16"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="16"/>
-      <c r="H61" s="17"/>
-      <c r="I61" s="18"/>
+      <c r="A61" s="68"/>
+      <c r="B61" s="69"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="68"/>
+      <c r="E61" s="69"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="68"/>
+      <c r="H61" s="69"/>
+      <c r="I61" s="70"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -2833,15 +2783,15 @@
       <c r="Z61" s="1"/>
     </row>
     <row r="62" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="16"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="16"/>
-      <c r="H62" s="17"/>
-      <c r="I62" s="18"/>
+      <c r="A62" s="68"/>
+      <c r="B62" s="69"/>
+      <c r="C62" s="70"/>
+      <c r="D62" s="68"/>
+      <c r="E62" s="69"/>
+      <c r="F62" s="70"/>
+      <c r="G62" s="68"/>
+      <c r="H62" s="69"/>
+      <c r="I62" s="70"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
@@ -2861,15 +2811,15 @@
       <c r="Z62" s="1"/>
     </row>
     <row r="63" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="16"/>
-      <c r="B63" s="17"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="18"/>
-      <c r="G63" s="16"/>
-      <c r="H63" s="17"/>
-      <c r="I63" s="18"/>
+      <c r="A63" s="68"/>
+      <c r="B63" s="69"/>
+      <c r="C63" s="70"/>
+      <c r="D63" s="68"/>
+      <c r="E63" s="69"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="68"/>
+      <c r="H63" s="69"/>
+      <c r="I63" s="70"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
@@ -2889,15 +2839,15 @@
       <c r="Z63" s="1"/>
     </row>
     <row r="64" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="16"/>
-      <c r="B64" s="17"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="18"/>
-      <c r="G64" s="16"/>
-      <c r="H64" s="17"/>
-      <c r="I64" s="18"/>
+      <c r="A64" s="68"/>
+      <c r="B64" s="69"/>
+      <c r="C64" s="70"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="69"/>
+      <c r="F64" s="70"/>
+      <c r="G64" s="68"/>
+      <c r="H64" s="69"/>
+      <c r="I64" s="70"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -2917,15 +2867,15 @@
       <c r="Z64" s="1"/>
     </row>
     <row r="65" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="16"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="20"/>
-      <c r="I65" s="21"/>
+      <c r="A65" s="68"/>
+      <c r="B65" s="69"/>
+      <c r="C65" s="70"/>
+      <c r="D65" s="68"/>
+      <c r="E65" s="69"/>
+      <c r="F65" s="70"/>
+      <c r="G65" s="68"/>
+      <c r="H65" s="69"/>
+      <c r="I65" s="70"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -2945,15 +2895,15 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="16"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15"/>
+      <c r="A66" s="68"/>
+      <c r="B66" s="69"/>
+      <c r="C66" s="70"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="69"/>
+      <c r="F66" s="70"/>
+      <c r="G66" s="68"/>
+      <c r="H66" s="69"/>
+      <c r="I66" s="70"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -2973,15 +2923,15 @@
       <c r="Z66" s="1"/>
     </row>
     <row r="67" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="16"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="18"/>
-      <c r="G67" s="16"/>
-      <c r="H67" s="17"/>
-      <c r="I67" s="18"/>
+      <c r="A67" s="68"/>
+      <c r="B67" s="69"/>
+      <c r="C67" s="70"/>
+      <c r="D67" s="71"/>
+      <c r="E67" s="72"/>
+      <c r="F67" s="73"/>
+      <c r="G67" s="71"/>
+      <c r="H67" s="72"/>
+      <c r="I67" s="73"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
@@ -3001,15 +2951,21 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="16"/>
-      <c r="B68" s="17"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="16"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="16"/>
-      <c r="H68" s="17"/>
-      <c r="I68" s="18"/>
+      <c r="A68" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" s="49"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="E68" s="49"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="H68" s="49"/>
+      <c r="I68" s="22"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
@@ -3029,15 +2985,15 @@
       <c r="Z68" s="1"/>
     </row>
     <row r="69" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="16"/>
-      <c r="B69" s="17"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="18"/>
-      <c r="G69" s="16"/>
-      <c r="H69" s="17"/>
-      <c r="I69" s="18"/>
+      <c r="A69" s="65"/>
+      <c r="B69" s="66"/>
+      <c r="C69" s="67"/>
+      <c r="D69" s="65"/>
+      <c r="E69" s="66"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="74"/>
+      <c r="H69" s="66"/>
+      <c r="I69" s="67"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
@@ -3057,15 +3013,15 @@
       <c r="Z69" s="1"/>
     </row>
     <row r="70" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="16"/>
-      <c r="B70" s="17"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="18"/>
-      <c r="G70" s="16"/>
-      <c r="H70" s="17"/>
-      <c r="I70" s="18"/>
+      <c r="A70" s="68"/>
+      <c r="B70" s="69"/>
+      <c r="C70" s="70"/>
+      <c r="D70" s="68"/>
+      <c r="E70" s="69"/>
+      <c r="F70" s="70"/>
+      <c r="G70" s="68"/>
+      <c r="H70" s="69"/>
+      <c r="I70" s="70"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
@@ -3085,15 +3041,15 @@
       <c r="Z70" s="1"/>
     </row>
     <row r="71" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="16"/>
-      <c r="B71" s="17"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="18"/>
-      <c r="G71" s="16"/>
-      <c r="H71" s="17"/>
-      <c r="I71" s="18"/>
+      <c r="A71" s="68"/>
+      <c r="B71" s="69"/>
+      <c r="C71" s="70"/>
+      <c r="D71" s="68"/>
+      <c r="E71" s="69"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="68"/>
+      <c r="H71" s="69"/>
+      <c r="I71" s="70"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
@@ -3113,15 +3069,15 @@
       <c r="Z71" s="1"/>
     </row>
     <row r="72" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="16"/>
-      <c r="B72" s="17"/>
-      <c r="C72" s="18"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="18"/>
-      <c r="G72" s="16"/>
-      <c r="H72" s="17"/>
-      <c r="I72" s="18"/>
+      <c r="A72" s="68"/>
+      <c r="B72" s="69"/>
+      <c r="C72" s="70"/>
+      <c r="D72" s="68"/>
+      <c r="E72" s="69"/>
+      <c r="F72" s="70"/>
+      <c r="G72" s="68"/>
+      <c r="H72" s="69"/>
+      <c r="I72" s="70"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
@@ -3141,15 +3097,15 @@
       <c r="Z72" s="1"/>
     </row>
     <row r="73" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="16"/>
-      <c r="B73" s="17"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="16"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="18"/>
-      <c r="G73" s="16"/>
-      <c r="H73" s="17"/>
-      <c r="I73" s="18"/>
+      <c r="A73" s="68"/>
+      <c r="B73" s="69"/>
+      <c r="C73" s="70"/>
+      <c r="D73" s="68"/>
+      <c r="E73" s="69"/>
+      <c r="F73" s="70"/>
+      <c r="G73" s="68"/>
+      <c r="H73" s="69"/>
+      <c r="I73" s="70"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
@@ -3169,15 +3125,15 @@
       <c r="Z73" s="1"/>
     </row>
     <row r="74" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="16"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="17"/>
-      <c r="F74" s="18"/>
-      <c r="G74" s="16"/>
-      <c r="H74" s="17"/>
-      <c r="I74" s="18"/>
+      <c r="A74" s="68"/>
+      <c r="B74" s="69"/>
+      <c r="C74" s="70"/>
+      <c r="D74" s="68"/>
+      <c r="E74" s="69"/>
+      <c r="F74" s="70"/>
+      <c r="G74" s="68"/>
+      <c r="H74" s="69"/>
+      <c r="I74" s="70"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
@@ -3197,15 +3153,15 @@
       <c r="Z74" s="1"/>
     </row>
     <row r="75" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="16"/>
-      <c r="B75" s="17"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="19"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="21"/>
+      <c r="A75" s="68"/>
+      <c r="B75" s="69"/>
+      <c r="C75" s="70"/>
+      <c r="D75" s="68"/>
+      <c r="E75" s="69"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="68"/>
+      <c r="H75" s="69"/>
+      <c r="I75" s="70"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
@@ -3225,21 +3181,15 @@
       <c r="Z75" s="1"/>
     </row>
     <row r="76" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="36"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="E76" s="36"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="H76" s="36"/>
-      <c r="I76" s="37"/>
+      <c r="A76" s="68"/>
+      <c r="B76" s="69"/>
+      <c r="C76" s="70"/>
+      <c r="D76" s="68"/>
+      <c r="E76" s="69"/>
+      <c r="F76" s="70"/>
+      <c r="G76" s="68"/>
+      <c r="H76" s="69"/>
+      <c r="I76" s="70"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
@@ -3259,15 +3209,15 @@
       <c r="Z76" s="1"/>
     </row>
     <row r="77" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="15"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="22"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15"/>
+      <c r="A77" s="68"/>
+      <c r="B77" s="69"/>
+      <c r="C77" s="70"/>
+      <c r="D77" s="68"/>
+      <c r="E77" s="69"/>
+      <c r="F77" s="70"/>
+      <c r="G77" s="68"/>
+      <c r="H77" s="69"/>
+      <c r="I77" s="70"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
@@ -3287,15 +3237,15 @@
       <c r="Z77" s="1"/>
     </row>
     <row r="78" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="16"/>
-      <c r="B78" s="17"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="16"/>
-      <c r="E78" s="17"/>
-      <c r="F78" s="18"/>
-      <c r="G78" s="16"/>
-      <c r="H78" s="17"/>
-      <c r="I78" s="18"/>
+      <c r="A78" s="68"/>
+      <c r="B78" s="69"/>
+      <c r="C78" s="70"/>
+      <c r="D78" s="71"/>
+      <c r="E78" s="72"/>
+      <c r="F78" s="73"/>
+      <c r="G78" s="71"/>
+      <c r="H78" s="72"/>
+      <c r="I78" s="73"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
@@ -3315,15 +3265,15 @@
       <c r="Z78" s="1"/>
     </row>
     <row r="79" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="16"/>
-      <c r="B79" s="17"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="18"/>
-      <c r="G79" s="16"/>
-      <c r="H79" s="17"/>
-      <c r="I79" s="18"/>
+      <c r="A79" s="68"/>
+      <c r="B79" s="69"/>
+      <c r="C79" s="70"/>
+      <c r="D79" s="65"/>
+      <c r="E79" s="66"/>
+      <c r="F79" s="67"/>
+      <c r="G79" s="65"/>
+      <c r="H79" s="66"/>
+      <c r="I79" s="67"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
@@ -3343,15 +3293,15 @@
       <c r="Z79" s="1"/>
     </row>
     <row r="80" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="16"/>
-      <c r="B80" s="17"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="18"/>
-      <c r="G80" s="16"/>
-      <c r="H80" s="17"/>
-      <c r="I80" s="18"/>
+      <c r="A80" s="68"/>
+      <c r="B80" s="69"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="68"/>
+      <c r="E80" s="69"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="68"/>
+      <c r="H80" s="69"/>
+      <c r="I80" s="70"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
@@ -3371,15 +3321,15 @@
       <c r="Z80" s="1"/>
     </row>
     <row r="81" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="16"/>
-      <c r="B81" s="17"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="16"/>
-      <c r="H81" s="17"/>
-      <c r="I81" s="18"/>
+      <c r="A81" s="68"/>
+      <c r="B81" s="69"/>
+      <c r="C81" s="70"/>
+      <c r="D81" s="68"/>
+      <c r="E81" s="69"/>
+      <c r="F81" s="70"/>
+      <c r="G81" s="68"/>
+      <c r="H81" s="69"/>
+      <c r="I81" s="70"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
@@ -3399,15 +3349,15 @@
       <c r="Z81" s="1"/>
     </row>
     <row r="82" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="16"/>
-      <c r="B82" s="17"/>
-      <c r="C82" s="18"/>
-      <c r="D82" s="16"/>
-      <c r="E82" s="17"/>
-      <c r="F82" s="18"/>
-      <c r="G82" s="16"/>
-      <c r="H82" s="17"/>
-      <c r="I82" s="18"/>
+      <c r="A82" s="68"/>
+      <c r="B82" s="69"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="68"/>
+      <c r="E82" s="69"/>
+      <c r="F82" s="70"/>
+      <c r="G82" s="68"/>
+      <c r="H82" s="69"/>
+      <c r="I82" s="70"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
@@ -3427,15 +3377,15 @@
       <c r="Z82" s="1"/>
     </row>
     <row r="83" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="16"/>
-      <c r="B83" s="17"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="18"/>
-      <c r="G83" s="16"/>
-      <c r="H83" s="17"/>
-      <c r="I83" s="18"/>
+      <c r="A83" s="68"/>
+      <c r="B83" s="69"/>
+      <c r="C83" s="70"/>
+      <c r="D83" s="68"/>
+      <c r="E83" s="69"/>
+      <c r="F83" s="70"/>
+      <c r="G83" s="68"/>
+      <c r="H83" s="69"/>
+      <c r="I83" s="70"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
@@ -3455,15 +3405,15 @@
       <c r="Z83" s="1"/>
     </row>
     <row r="84" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="16"/>
-      <c r="B84" s="17"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="16"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="18"/>
-      <c r="G84" s="16"/>
-      <c r="H84" s="17"/>
-      <c r="I84" s="18"/>
+      <c r="A84" s="68"/>
+      <c r="B84" s="69"/>
+      <c r="C84" s="70"/>
+      <c r="D84" s="68"/>
+      <c r="E84" s="69"/>
+      <c r="F84" s="70"/>
+      <c r="G84" s="68"/>
+      <c r="H84" s="69"/>
+      <c r="I84" s="70"/>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
@@ -3483,15 +3433,15 @@
       <c r="Z84" s="1"/>
     </row>
     <row r="85" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="16"/>
-      <c r="B85" s="17"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="16"/>
-      <c r="E85" s="17"/>
-      <c r="F85" s="18"/>
-      <c r="G85" s="16"/>
-      <c r="H85" s="17"/>
-      <c r="I85" s="18"/>
+      <c r="A85" s="68"/>
+      <c r="B85" s="69"/>
+      <c r="C85" s="70"/>
+      <c r="D85" s="68"/>
+      <c r="E85" s="69"/>
+      <c r="F85" s="70"/>
+      <c r="G85" s="68"/>
+      <c r="H85" s="69"/>
+      <c r="I85" s="70"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
@@ -3511,15 +3461,15 @@
       <c r="Z85" s="1"/>
     </row>
     <row r="86" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="16"/>
-      <c r="B86" s="17"/>
-      <c r="C86" s="18"/>
-      <c r="D86" s="19"/>
-      <c r="E86" s="20"/>
-      <c r="F86" s="21"/>
-      <c r="G86" s="19"/>
-      <c r="H86" s="20"/>
-      <c r="I86" s="21"/>
+      <c r="A86" s="68"/>
+      <c r="B86" s="69"/>
+      <c r="C86" s="70"/>
+      <c r="D86" s="68"/>
+      <c r="E86" s="69"/>
+      <c r="F86" s="70"/>
+      <c r="G86" s="68"/>
+      <c r="H86" s="69"/>
+      <c r="I86" s="70"/>
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
@@ -3539,15 +3489,15 @@
       <c r="Z86" s="1"/>
     </row>
     <row r="87" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="16"/>
-      <c r="B87" s="17"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="13"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="15"/>
-      <c r="G87" s="13"/>
-      <c r="H87" s="14"/>
-      <c r="I87" s="15"/>
+      <c r="A87" s="68"/>
+      <c r="B87" s="69"/>
+      <c r="C87" s="70"/>
+      <c r="D87" s="68"/>
+      <c r="E87" s="69"/>
+      <c r="F87" s="70"/>
+      <c r="G87" s="68"/>
+      <c r="H87" s="69"/>
+      <c r="I87" s="70"/>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
@@ -3567,15 +3517,15 @@
       <c r="Z87" s="1"/>
     </row>
     <row r="88" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="16"/>
-      <c r="B88" s="17"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="16"/>
-      <c r="E88" s="17"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="16"/>
-      <c r="H88" s="17"/>
-      <c r="I88" s="18"/>
+      <c r="A88" s="71"/>
+      <c r="B88" s="72"/>
+      <c r="C88" s="73"/>
+      <c r="D88" s="71"/>
+      <c r="E88" s="72"/>
+      <c r="F88" s="73"/>
+      <c r="G88" s="71"/>
+      <c r="H88" s="72"/>
+      <c r="I88" s="73"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
@@ -3595,15 +3545,21 @@
       <c r="Z88" s="1"/>
     </row>
     <row r="89" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="16"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="16"/>
-      <c r="E89" s="17"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="16"/>
-      <c r="H89" s="17"/>
-      <c r="I89" s="18"/>
+      <c r="A89" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="B89" s="49"/>
+      <c r="C89" s="22"/>
+      <c r="D89" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="E89" s="49"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="H89" s="49"/>
+      <c r="I89" s="22"/>
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
@@ -3623,15 +3579,15 @@
       <c r="Z89" s="1"/>
     </row>
     <row r="90" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="16"/>
-      <c r="B90" s="17"/>
-      <c r="C90" s="18"/>
-      <c r="D90" s="16"/>
-      <c r="E90" s="17"/>
-      <c r="F90" s="18"/>
-      <c r="G90" s="16"/>
-      <c r="H90" s="17"/>
-      <c r="I90" s="18"/>
+      <c r="A90" s="52"/>
+      <c r="B90" s="53"/>
+      <c r="C90" s="53"/>
+      <c r="D90" s="53"/>
+      <c r="E90" s="53"/>
+      <c r="F90" s="53"/>
+      <c r="G90" s="53"/>
+      <c r="H90" s="53"/>
+      <c r="I90" s="53"/>
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
       <c r="L90" s="1"/>
@@ -3651,15 +3607,19 @@
       <c r="Z90" s="1"/>
     </row>
     <row r="91" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="16"/>
+      <c r="A91" s="54" t="s">
+        <v>38</v>
+      </c>
       <c r="B91" s="17"/>
       <c r="C91" s="18"/>
-      <c r="D91" s="16"/>
-      <c r="E91" s="17"/>
-      <c r="F91" s="18"/>
-      <c r="G91" s="16"/>
-      <c r="H91" s="17"/>
-      <c r="I91" s="18"/>
+      <c r="D91" s="55"/>
+      <c r="E91" s="53"/>
+      <c r="F91" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="G91" s="53"/>
+      <c r="H91" s="53"/>
+      <c r="I91" s="57"/>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
@@ -3679,15 +3639,25 @@
       <c r="Z91" s="1"/>
     </row>
     <row r="92" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="16"/>
-      <c r="B92" s="17"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="16"/>
-      <c r="E92" s="17"/>
-      <c r="F92" s="18"/>
-      <c r="G92" s="16"/>
-      <c r="H92" s="17"/>
-      <c r="I92" s="18"/>
+      <c r="A92" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D92" s="53"/>
+      <c r="E92" s="53"/>
+      <c r="F92" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G92" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="H92" s="49"/>
+      <c r="I92" s="22"/>
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
@@ -3707,15 +3677,17 @@
       <c r="Z92" s="1"/>
     </row>
     <row r="93" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="16"/>
-      <c r="B93" s="17"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="16"/>
-      <c r="E93" s="17"/>
-      <c r="F93" s="18"/>
-      <c r="G93" s="16"/>
-      <c r="H93" s="17"/>
-      <c r="I93" s="18"/>
+      <c r="A93" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B93" s="11"/>
+      <c r="C93" s="11"/>
+      <c r="D93" s="53"/>
+      <c r="E93" s="53"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="58"/>
+      <c r="H93" s="49"/>
+      <c r="I93" s="22"/>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
@@ -3735,15 +3707,17 @@
       <c r="Z93" s="1"/>
     </row>
     <row r="94" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="16"/>
-      <c r="B94" s="17"/>
-      <c r="C94" s="18"/>
-      <c r="D94" s="16"/>
-      <c r="E94" s="17"/>
-      <c r="F94" s="18"/>
-      <c r="G94" s="16"/>
-      <c r="H94" s="17"/>
-      <c r="I94" s="18"/>
+      <c r="A94" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B94" s="11"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="53"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="58"/>
+      <c r="H94" s="49"/>
+      <c r="I94" s="22"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
@@ -3763,15 +3737,17 @@
       <c r="Z94" s="1"/>
     </row>
     <row r="95" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="16"/>
-      <c r="B95" s="17"/>
-      <c r="C95" s="18"/>
-      <c r="D95" s="16"/>
-      <c r="E95" s="17"/>
-      <c r="F95" s="18"/>
-      <c r="G95" s="16"/>
-      <c r="H95" s="17"/>
-      <c r="I95" s="18"/>
+      <c r="A95" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B95" s="11"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="53"/>
+      <c r="E95" s="53"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="58"/>
+      <c r="H95" s="49"/>
+      <c r="I95" s="22"/>
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
@@ -3791,15 +3767,17 @@
       <c r="Z95" s="1"/>
     </row>
     <row r="96" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="19"/>
-      <c r="B96" s="20"/>
-      <c r="C96" s="21"/>
-      <c r="D96" s="19"/>
-      <c r="E96" s="20"/>
-      <c r="F96" s="21"/>
-      <c r="G96" s="19"/>
-      <c r="H96" s="20"/>
-      <c r="I96" s="21"/>
+      <c r="A96" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B96" s="59"/>
+      <c r="C96" s="22"/>
+      <c r="D96" s="53"/>
+      <c r="E96" s="53"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="58"/>
+      <c r="H96" s="49"/>
+      <c r="I96" s="22"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
@@ -3819,21 +3797,15 @@
       <c r="Z96" s="1"/>
     </row>
     <row r="97" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B97" s="36"/>
-      <c r="C97" s="37"/>
-      <c r="D97" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="E97" s="36"/>
-      <c r="F97" s="37"/>
-      <c r="G97" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="H97" s="36"/>
-      <c r="I97" s="37"/>
+      <c r="A97" s="60"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14"/>
+      <c r="D97" s="53"/>
+      <c r="E97" s="53"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="58"/>
+      <c r="H97" s="49"/>
+      <c r="I97" s="22"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
@@ -3853,15 +3825,17 @@
       <c r="Z97" s="1"/>
     </row>
     <row r="98" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="51"/>
-      <c r="B98" s="52"/>
-      <c r="C98" s="52"/>
-      <c r="D98" s="52"/>
-      <c r="E98" s="52"/>
-      <c r="F98" s="52"/>
-      <c r="G98" s="52"/>
-      <c r="H98" s="52"/>
-      <c r="I98" s="52"/>
+      <c r="A98" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="B98" s="14"/>
+      <c r="C98" s="14"/>
+      <c r="D98" s="14"/>
+      <c r="E98" s="14"/>
+      <c r="F98" s="14"/>
+      <c r="G98" s="14"/>
+      <c r="H98" s="14"/>
+      <c r="I98" s="15"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
@@ -3881,19 +3855,23 @@
       <c r="Z98" s="1"/>
     </row>
     <row r="99" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="53" t="s">
-        <v>46</v>
+      <c r="A99" s="3" t="s">
+        <v>49</v>
       </c>
-      <c r="B99" s="27"/>
-      <c r="C99" s="28"/>
-      <c r="D99" s="54"/>
-      <c r="E99" s="52"/>
-      <c r="F99" s="55" t="s">
-        <v>47</v>
+      <c r="B99" s="21" t="s">
+        <v>50</v>
       </c>
-      <c r="G99" s="52"/>
-      <c r="H99" s="52"/>
-      <c r="I99" s="31"/>
+      <c r="C99" s="49"/>
+      <c r="D99" s="49"/>
+      <c r="E99" s="49"/>
+      <c r="F99" s="49"/>
+      <c r="G99" s="49"/>
+      <c r="H99" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
@@ -3913,25 +3891,19 @@
       <c r="Z99" s="1"/>
     </row>
     <row r="100" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="9" t="s">
-        <v>48</v>
+      <c r="A100" s="12">
+        <v>1</v>
       </c>
-      <c r="B100" s="10" t="s">
-        <v>49</v>
+      <c r="B100" s="62" t="s">
+        <v>53</v>
       </c>
-      <c r="C100" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D100" s="52"/>
-      <c r="E100" s="52"/>
-      <c r="F100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G100" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="H100" s="36"/>
-      <c r="I100" s="37"/>
+      <c r="C100" s="49"/>
+      <c r="D100" s="49"/>
+      <c r="E100" s="49"/>
+      <c r="F100" s="49"/>
+      <c r="G100" s="22"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
       <c r="L100" s="1"/>
@@ -3951,17 +3923,19 @@
       <c r="Z100" s="1"/>
     </row>
     <row r="101" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="9" t="s">
-        <v>52</v>
+      <c r="A101" s="12">
+        <v>2</v>
       </c>
-      <c r="B101" s="11"/>
-      <c r="C101" s="11"/>
-      <c r="D101" s="52"/>
-      <c r="E101" s="52"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="56"/>
-      <c r="H101" s="36"/>
-      <c r="I101" s="37"/>
+      <c r="B101" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="C101" s="49"/>
+      <c r="D101" s="49"/>
+      <c r="E101" s="49"/>
+      <c r="F101" s="49"/>
+      <c r="G101" s="22"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="6"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -3981,17 +3955,19 @@
       <c r="Z101" s="1"/>
     </row>
     <row r="102" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="9" t="s">
-        <v>53</v>
+      <c r="A102" s="12">
+        <v>3</v>
       </c>
-      <c r="B102" s="11"/>
-      <c r="C102" s="11"/>
-      <c r="D102" s="52"/>
-      <c r="E102" s="52"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="56"/>
-      <c r="H102" s="36"/>
-      <c r="I102" s="37"/>
+      <c r="B102" s="62" t="s">
+        <v>55</v>
+      </c>
+      <c r="C102" s="49"/>
+      <c r="D102" s="49"/>
+      <c r="E102" s="49"/>
+      <c r="F102" s="49"/>
+      <c r="G102" s="22"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6"/>
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
@@ -4011,17 +3987,19 @@
       <c r="Z102" s="1"/>
     </row>
     <row r="103" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="9" t="s">
-        <v>54</v>
+      <c r="A103" s="12">
+        <v>4</v>
       </c>
-      <c r="B103" s="11"/>
-      <c r="C103" s="11"/>
-      <c r="D103" s="52"/>
-      <c r="E103" s="52"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="56"/>
-      <c r="H103" s="36"/>
-      <c r="I103" s="37"/>
+      <c r="B103" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="C103" s="49"/>
+      <c r="D103" s="49"/>
+      <c r="E103" s="49"/>
+      <c r="F103" s="49"/>
+      <c r="G103" s="22"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -4041,17 +4019,19 @@
       <c r="Z103" s="1"/>
     </row>
     <row r="104" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="9" t="s">
-        <v>55</v>
+      <c r="A104" s="12">
+        <v>5</v>
       </c>
-      <c r="B104" s="57"/>
-      <c r="C104" s="37"/>
-      <c r="D104" s="52"/>
-      <c r="E104" s="52"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="56"/>
-      <c r="H104" s="36"/>
-      <c r="I104" s="37"/>
+      <c r="B104" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="C104" s="49"/>
+      <c r="D104" s="49"/>
+      <c r="E104" s="49"/>
+      <c r="F104" s="49"/>
+      <c r="G104" s="22"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="6"/>
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
@@ -4071,15 +4051,19 @@
       <c r="Z104" s="1"/>
     </row>
     <row r="105" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="58"/>
-      <c r="B105" s="24"/>
-      <c r="C105" s="24"/>
-      <c r="D105" s="52"/>
-      <c r="E105" s="52"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="56"/>
-      <c r="H105" s="36"/>
-      <c r="I105" s="37"/>
+      <c r="A105" s="12">
+        <v>6</v>
+      </c>
+      <c r="B105" s="62" t="s">
+        <v>58</v>
+      </c>
+      <c r="C105" s="49"/>
+      <c r="D105" s="49"/>
+      <c r="E105" s="49"/>
+      <c r="F105" s="49"/>
+      <c r="G105" s="22"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -4099,17 +4083,19 @@
       <c r="Z105" s="1"/>
     </row>
     <row r="106" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="59" t="s">
-        <v>56</v>
+      <c r="A106" s="12">
+        <v>7</v>
       </c>
-      <c r="B106" s="24"/>
-      <c r="C106" s="24"/>
-      <c r="D106" s="24"/>
-      <c r="E106" s="24"/>
-      <c r="F106" s="24"/>
-      <c r="G106" s="24"/>
-      <c r="H106" s="24"/>
-      <c r="I106" s="25"/>
+      <c r="B106" s="62" t="s">
+        <v>59</v>
+      </c>
+      <c r="C106" s="49"/>
+      <c r="D106" s="49"/>
+      <c r="E106" s="49"/>
+      <c r="F106" s="49"/>
+      <c r="G106" s="22"/>
+      <c r="H106" s="6"/>
+      <c r="I106" s="6"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -4129,23 +4115,19 @@
       <c r="Z106" s="1"/>
     </row>
     <row r="107" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="3" t="s">
-        <v>57</v>
+      <c r="A107" s="12">
+        <v>8</v>
       </c>
-      <c r="B107" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="C107" s="36"/>
-      <c r="D107" s="36"/>
-      <c r="E107" s="36"/>
-      <c r="F107" s="36"/>
-      <c r="G107" s="36"/>
-      <c r="H107" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I107" s="3" t="s">
+      <c r="B107" s="62" t="s">
         <v>60</v>
       </c>
+      <c r="C107" s="49"/>
+      <c r="D107" s="49"/>
+      <c r="E107" s="49"/>
+      <c r="F107" s="49"/>
+      <c r="G107" s="22"/>
+      <c r="H107" s="6"/>
+      <c r="I107" s="6"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
@@ -4166,16 +4148,16 @@
     </row>
     <row r="108" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12">
-        <v>1</v>
+        <v>9</v>
       </c>
-      <c r="B108" s="60" t="s">
+      <c r="B108" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="C108" s="36"/>
-      <c r="D108" s="36"/>
-      <c r="E108" s="36"/>
-      <c r="F108" s="36"/>
-      <c r="G108" s="37"/>
+      <c r="C108" s="49"/>
+      <c r="D108" s="49"/>
+      <c r="E108" s="49"/>
+      <c r="F108" s="49"/>
+      <c r="G108" s="22"/>
       <c r="H108" s="6"/>
       <c r="I108" s="6"/>
       <c r="J108" s="1"/>
@@ -4198,16 +4180,16 @@
     </row>
     <row r="109" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="12">
-        <v>2</v>
+        <v>10</v>
       </c>
-      <c r="B109" s="60" t="s">
+      <c r="B109" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="C109" s="36"/>
-      <c r="D109" s="36"/>
-      <c r="E109" s="36"/>
-      <c r="F109" s="36"/>
-      <c r="G109" s="37"/>
+      <c r="C109" s="49"/>
+      <c r="D109" s="49"/>
+      <c r="E109" s="49"/>
+      <c r="F109" s="49"/>
+      <c r="G109" s="22"/>
       <c r="H109" s="6"/>
       <c r="I109" s="6"/>
       <c r="J109" s="1"/>
@@ -4230,16 +4212,16 @@
     </row>
     <row r="110" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12">
-        <v>3</v>
+        <v>11</v>
       </c>
-      <c r="B110" s="60" t="s">
+      <c r="B110" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="C110" s="36"/>
-      <c r="D110" s="36"/>
-      <c r="E110" s="36"/>
-      <c r="F110" s="36"/>
-      <c r="G110" s="37"/>
+      <c r="C110" s="49"/>
+      <c r="D110" s="49"/>
+      <c r="E110" s="49"/>
+      <c r="F110" s="49"/>
+      <c r="G110" s="22"/>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
       <c r="J110" s="1"/>
@@ -4262,16 +4244,16 @@
     </row>
     <row r="111" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="12">
-        <v>4</v>
+        <v>12</v>
       </c>
-      <c r="B111" s="60" t="s">
+      <c r="B111" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36"/>
-      <c r="G111" s="37"/>
+      <c r="C111" s="49"/>
+      <c r="D111" s="49"/>
+      <c r="E111" s="49"/>
+      <c r="F111" s="49"/>
+      <c r="G111" s="22"/>
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
       <c r="J111" s="1"/>
@@ -4294,16 +4276,16 @@
     </row>
     <row r="112" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12">
-        <v>5</v>
+        <v>13</v>
       </c>
-      <c r="B112" s="60" t="s">
+      <c r="B112" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="C112" s="36"/>
-      <c r="D112" s="36"/>
-      <c r="E112" s="36"/>
-      <c r="F112" s="36"/>
-      <c r="G112" s="37"/>
+      <c r="C112" s="49"/>
+      <c r="D112" s="49"/>
+      <c r="E112" s="49"/>
+      <c r="F112" s="49"/>
+      <c r="G112" s="22"/>
       <c r="H112" s="6"/>
       <c r="I112" s="6"/>
       <c r="J112" s="1"/>
@@ -4325,19 +4307,17 @@
       <c r="Z112" s="1"/>
     </row>
     <row r="113" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="12">
-        <v>6</v>
+      <c r="A113" s="43" t="s">
+        <v>47</v>
       </c>
-      <c r="B113" s="60" t="s">
-        <v>66</v>
-      </c>
-      <c r="C113" s="36"/>
-      <c r="D113" s="36"/>
-      <c r="E113" s="36"/>
-      <c r="F113" s="36"/>
-      <c r="G113" s="37"/>
-      <c r="H113" s="6"/>
-      <c r="I113" s="6"/>
+      <c r="B113" s="14"/>
+      <c r="C113" s="14"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="14"/>
+      <c r="F113" s="14"/>
+      <c r="G113" s="14"/>
+      <c r="H113" s="14"/>
+      <c r="I113" s="15"/>
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
@@ -4357,19 +4337,15 @@
       <c r="Z113" s="1"/>
     </row>
     <row r="114" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="12">
-        <v>7</v>
-      </c>
-      <c r="B114" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="C114" s="36"/>
-      <c r="D114" s="36"/>
-      <c r="E114" s="36"/>
-      <c r="F114" s="36"/>
-      <c r="G114" s="37"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
+      <c r="A114" s="63"/>
+      <c r="B114" s="14"/>
+      <c r="C114" s="14"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="14"/>
+      <c r="F114" s="14"/>
+      <c r="G114" s="14"/>
+      <c r="H114" s="14"/>
+      <c r="I114" s="15"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
       <c r="L114" s="1"/>
@@ -4389,19 +4365,17 @@
       <c r="Z114" s="1"/>
     </row>
     <row r="115" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="12">
-        <v>8</v>
+      <c r="A115" s="43" t="s">
+        <v>66</v>
       </c>
-      <c r="B115" s="60" t="s">
-        <v>68</v>
-      </c>
-      <c r="C115" s="36"/>
-      <c r="D115" s="36"/>
-      <c r="E115" s="36"/>
-      <c r="F115" s="36"/>
-      <c r="G115" s="37"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
+      <c r="B115" s="14"/>
+      <c r="C115" s="14"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="14"/>
+      <c r="F115" s="14"/>
+      <c r="G115" s="14"/>
+      <c r="H115" s="14"/>
+      <c r="I115" s="15"/>
       <c r="J115" s="1"/>
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
@@ -4421,19 +4395,15 @@
       <c r="Z115" s="1"/>
     </row>
     <row r="116" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="12">
-        <v>9</v>
-      </c>
-      <c r="B116" s="60" t="s">
-        <v>69</v>
-      </c>
-      <c r="C116" s="36"/>
-      <c r="D116" s="36"/>
-      <c r="E116" s="36"/>
-      <c r="F116" s="36"/>
-      <c r="G116" s="37"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6"/>
+      <c r="A116" s="63"/>
+      <c r="B116" s="14"/>
+      <c r="C116" s="14"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="14"/>
+      <c r="F116" s="14"/>
+      <c r="G116" s="14"/>
+      <c r="H116" s="14"/>
+      <c r="I116" s="15"/>
       <c r="J116" s="1"/>
       <c r="K116" s="1"/>
       <c r="L116" s="1"/>
@@ -4453,19 +4423,15 @@
       <c r="Z116" s="1"/>
     </row>
     <row r="117" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="12">
-        <v>10</v>
-      </c>
-      <c r="B117" s="60" t="s">
-        <v>70</v>
-      </c>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-      <c r="G117" s="37"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="6"/>
+      <c r="A117" s="63"/>
+      <c r="B117" s="14"/>
+      <c r="C117" s="14"/>
+      <c r="D117" s="14"/>
+      <c r="E117" s="14"/>
+      <c r="F117" s="14"/>
+      <c r="G117" s="14"/>
+      <c r="H117" s="14"/>
+      <c r="I117" s="15"/>
       <c r="J117" s="1"/>
       <c r="K117" s="1"/>
       <c r="L117" s="1"/>
@@ -4485,19 +4451,15 @@
       <c r="Z117" s="1"/>
     </row>
     <row r="118" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="12">
-        <v>11</v>
-      </c>
-      <c r="B118" s="60" t="s">
-        <v>71</v>
-      </c>
-      <c r="C118" s="36"/>
-      <c r="D118" s="36"/>
-      <c r="E118" s="36"/>
-      <c r="F118" s="36"/>
-      <c r="G118" s="37"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
+      <c r="A118" s="63"/>
+      <c r="B118" s="14"/>
+      <c r="C118" s="14"/>
+      <c r="D118" s="14"/>
+      <c r="E118" s="14"/>
+      <c r="F118" s="14"/>
+      <c r="G118" s="14"/>
+      <c r="H118" s="14"/>
+      <c r="I118" s="15"/>
       <c r="J118" s="1"/>
       <c r="K118" s="1"/>
       <c r="L118" s="1"/>
@@ -4517,19 +4479,17 @@
       <c r="Z118" s="1"/>
     </row>
     <row r="119" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="12">
-        <v>12</v>
+      <c r="A119" s="43" t="s">
+        <v>67</v>
       </c>
-      <c r="B119" s="60" t="s">
-        <v>72</v>
-      </c>
-      <c r="C119" s="36"/>
-      <c r="D119" s="36"/>
-      <c r="E119" s="36"/>
-      <c r="F119" s="36"/>
-      <c r="G119" s="37"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
+      <c r="B119" s="14"/>
+      <c r="C119" s="14"/>
+      <c r="D119" s="14"/>
+      <c r="E119" s="14"/>
+      <c r="F119" s="14"/>
+      <c r="G119" s="14"/>
+      <c r="H119" s="14"/>
+      <c r="I119" s="15"/>
       <c r="J119" s="1"/>
       <c r="K119" s="1"/>
       <c r="L119" s="1"/>
@@ -4549,19 +4509,15 @@
       <c r="Z119" s="1"/>
     </row>
     <row r="120" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="12">
-        <v>13</v>
-      </c>
-      <c r="B120" s="60" t="s">
-        <v>73</v>
-      </c>
-      <c r="C120" s="36"/>
-      <c r="D120" s="36"/>
-      <c r="E120" s="36"/>
-      <c r="F120" s="36"/>
-      <c r="G120" s="37"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
+      <c r="A120" s="64"/>
+      <c r="B120" s="49"/>
+      <c r="C120" s="49"/>
+      <c r="D120" s="49"/>
+      <c r="E120" s="49"/>
+      <c r="F120" s="49"/>
+      <c r="G120" s="49"/>
+      <c r="H120" s="49"/>
+      <c r="I120" s="22"/>
       <c r="J120" s="1"/>
       <c r="K120" s="1"/>
       <c r="L120" s="1"/>
@@ -4581,17 +4537,15 @@
       <c r="Z120" s="1"/>
     </row>
     <row r="121" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="B121" s="24"/>
-      <c r="C121" s="24"/>
-      <c r="D121" s="24"/>
-      <c r="E121" s="24"/>
-      <c r="F121" s="24"/>
-      <c r="G121" s="24"/>
-      <c r="H121" s="24"/>
-      <c r="I121" s="25"/>
+      <c r="A121" s="64"/>
+      <c r="B121" s="49"/>
+      <c r="C121" s="49"/>
+      <c r="D121" s="49"/>
+      <c r="E121" s="49"/>
+      <c r="F121" s="49"/>
+      <c r="G121" s="49"/>
+      <c r="H121" s="49"/>
+      <c r="I121" s="22"/>
       <c r="J121" s="1"/>
       <c r="K121" s="1"/>
       <c r="L121" s="1"/>
@@ -4611,15 +4565,15 @@
       <c r="Z121" s="1"/>
     </row>
     <row r="122" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="61"/>
-      <c r="B122" s="24"/>
-      <c r="C122" s="24"/>
-      <c r="D122" s="24"/>
-      <c r="E122" s="24"/>
-      <c r="F122" s="24"/>
-      <c r="G122" s="24"/>
-      <c r="H122" s="24"/>
-      <c r="I122" s="25"/>
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
       <c r="J122" s="1"/>
       <c r="K122" s="1"/>
       <c r="L122" s="1"/>
@@ -4639,17 +4593,15 @@
       <c r="Z122" s="1"/>
     </row>
     <row r="123" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="B123" s="24"/>
-      <c r="C123" s="24"/>
-      <c r="D123" s="24"/>
-      <c r="E123" s="24"/>
-      <c r="F123" s="24"/>
-      <c r="G123" s="24"/>
-      <c r="H123" s="24"/>
-      <c r="I123" s="25"/>
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1"/>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
       <c r="J123" s="1"/>
       <c r="K123" s="1"/>
       <c r="L123" s="1"/>
@@ -4669,15 +4621,15 @@
       <c r="Z123" s="1"/>
     </row>
     <row r="124" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="61"/>
-      <c r="B124" s="24"/>
-      <c r="C124" s="24"/>
-      <c r="D124" s="24"/>
-      <c r="E124" s="24"/>
-      <c r="F124" s="24"/>
-      <c r="G124" s="24"/>
-      <c r="H124" s="24"/>
-      <c r="I124" s="25"/>
+      <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1"/>
+      <c r="F124" s="1"/>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
       <c r="J124" s="1"/>
       <c r="K124" s="1"/>
       <c r="L124" s="1"/>
@@ -4697,15 +4649,15 @@
       <c r="Z124" s="1"/>
     </row>
     <row r="125" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="61"/>
-      <c r="B125" s="24"/>
-      <c r="C125" s="24"/>
-      <c r="D125" s="24"/>
-      <c r="E125" s="24"/>
-      <c r="F125" s="24"/>
-      <c r="G125" s="24"/>
-      <c r="H125" s="24"/>
-      <c r="I125" s="25"/>
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1"/>
+      <c r="F125" s="1"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
       <c r="J125" s="1"/>
       <c r="K125" s="1"/>
       <c r="L125" s="1"/>
@@ -4725,15 +4677,15 @@
       <c r="Z125" s="1"/>
     </row>
     <row r="126" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="61"/>
-      <c r="B126" s="24"/>
-      <c r="C126" s="24"/>
-      <c r="D126" s="24"/>
-      <c r="E126" s="24"/>
-      <c r="F126" s="24"/>
-      <c r="G126" s="24"/>
-      <c r="H126" s="24"/>
-      <c r="I126" s="25"/>
+      <c r="A126" s="1"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
       <c r="J126" s="1"/>
       <c r="K126" s="1"/>
       <c r="L126" s="1"/>
@@ -4753,17 +4705,15 @@
       <c r="Z126" s="1"/>
     </row>
     <row r="127" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="B127" s="24"/>
-      <c r="C127" s="24"/>
-      <c r="D127" s="24"/>
-      <c r="E127" s="24"/>
-      <c r="F127" s="24"/>
-      <c r="G127" s="24"/>
-      <c r="H127" s="24"/>
-      <c r="I127" s="25"/>
+      <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
+      <c r="E127" s="1"/>
+      <c r="F127" s="1"/>
+      <c r="G127" s="1"/>
+      <c r="H127" s="1"/>
+      <c r="I127" s="1"/>
       <c r="J127" s="1"/>
       <c r="K127" s="1"/>
       <c r="L127" s="1"/>
@@ -4783,15 +4733,15 @@
       <c r="Z127" s="1"/>
     </row>
     <row r="128" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="62"/>
-      <c r="B128" s="36"/>
-      <c r="C128" s="36"/>
-      <c r="D128" s="36"/>
-      <c r="E128" s="36"/>
-      <c r="F128" s="36"/>
-      <c r="G128" s="36"/>
-      <c r="H128" s="36"/>
-      <c r="I128" s="37"/>
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
@@ -4811,15 +4761,15 @@
       <c r="Z128" s="1"/>
     </row>
     <row r="129" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="62"/>
-      <c r="B129" s="36"/>
-      <c r="C129" s="36"/>
-      <c r="D129" s="36"/>
-      <c r="E129" s="36"/>
-      <c r="F129" s="36"/>
-      <c r="G129" s="36"/>
-      <c r="H129" s="36"/>
-      <c r="I129" s="37"/>
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
       <c r="J129" s="1"/>
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
@@ -10718,308 +10668,77 @@
       <c r="Y339" s="1"/>
       <c r="Z339" s="1"/>
     </row>
-    <row r="340" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A340" s="1"/>
-      <c r="B340" s="1"/>
-      <c r="C340" s="1"/>
-      <c r="D340" s="1"/>
-      <c r="E340" s="1"/>
-      <c r="F340" s="1"/>
-      <c r="G340" s="1"/>
-      <c r="H340" s="1"/>
-      <c r="I340" s="1"/>
-      <c r="J340" s="1"/>
-      <c r="K340" s="1"/>
-      <c r="L340" s="1"/>
-      <c r="M340" s="1"/>
-      <c r="N340" s="1"/>
-      <c r="O340" s="1"/>
-      <c r="P340" s="1"/>
-      <c r="Q340" s="1"/>
-      <c r="R340" s="1"/>
-      <c r="S340" s="1"/>
-      <c r="T340" s="1"/>
-      <c r="U340" s="1"/>
-      <c r="V340" s="1"/>
-      <c r="W340" s="1"/>
-      <c r="X340" s="1"/>
-      <c r="Y340" s="1"/>
-      <c r="Z340" s="1"/>
-    </row>
-    <row r="341" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A341" s="1"/>
-      <c r="B341" s="1"/>
-      <c r="C341" s="1"/>
-      <c r="D341" s="1"/>
-      <c r="E341" s="1"/>
-      <c r="F341" s="1"/>
-      <c r="G341" s="1"/>
-      <c r="H341" s="1"/>
-      <c r="I341" s="1"/>
-      <c r="J341" s="1"/>
-      <c r="K341" s="1"/>
-      <c r="L341" s="1"/>
-      <c r="M341" s="1"/>
-      <c r="N341" s="1"/>
-      <c r="O341" s="1"/>
-      <c r="P341" s="1"/>
-      <c r="Q341" s="1"/>
-      <c r="R341" s="1"/>
-      <c r="S341" s="1"/>
-      <c r="T341" s="1"/>
-      <c r="U341" s="1"/>
-      <c r="V341" s="1"/>
-      <c r="W341" s="1"/>
-      <c r="X341" s="1"/>
-      <c r="Y341" s="1"/>
-      <c r="Z341" s="1"/>
-    </row>
-    <row r="342" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A342" s="1"/>
-      <c r="B342" s="1"/>
-      <c r="C342" s="1"/>
-      <c r="D342" s="1"/>
-      <c r="E342" s="1"/>
-      <c r="F342" s="1"/>
-      <c r="G342" s="1"/>
-      <c r="H342" s="1"/>
-      <c r="I342" s="1"/>
-      <c r="J342" s="1"/>
-      <c r="K342" s="1"/>
-      <c r="L342" s="1"/>
-      <c r="M342" s="1"/>
-      <c r="N342" s="1"/>
-      <c r="O342" s="1"/>
-      <c r="P342" s="1"/>
-      <c r="Q342" s="1"/>
-      <c r="R342" s="1"/>
-      <c r="S342" s="1"/>
-      <c r="T342" s="1"/>
-      <c r="U342" s="1"/>
-      <c r="V342" s="1"/>
-      <c r="W342" s="1"/>
-      <c r="X342" s="1"/>
-      <c r="Y342" s="1"/>
-      <c r="Z342" s="1"/>
-    </row>
-    <row r="343" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A343" s="1"/>
-      <c r="B343" s="1"/>
-      <c r="C343" s="1"/>
-      <c r="D343" s="1"/>
-      <c r="E343" s="1"/>
-      <c r="F343" s="1"/>
-      <c r="G343" s="1"/>
-      <c r="H343" s="1"/>
-      <c r="I343" s="1"/>
-      <c r="J343" s="1"/>
-      <c r="K343" s="1"/>
-      <c r="L343" s="1"/>
-      <c r="M343" s="1"/>
-      <c r="N343" s="1"/>
-      <c r="O343" s="1"/>
-      <c r="P343" s="1"/>
-      <c r="Q343" s="1"/>
-      <c r="R343" s="1"/>
-      <c r="S343" s="1"/>
-      <c r="T343" s="1"/>
-      <c r="U343" s="1"/>
-      <c r="V343" s="1"/>
-      <c r="W343" s="1"/>
-      <c r="X343" s="1"/>
-      <c r="Y343" s="1"/>
-      <c r="Z343" s="1"/>
-    </row>
-    <row r="344" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A344" s="1"/>
-      <c r="B344" s="1"/>
-      <c r="C344" s="1"/>
-      <c r="D344" s="1"/>
-      <c r="E344" s="1"/>
-      <c r="F344" s="1"/>
-      <c r="G344" s="1"/>
-      <c r="H344" s="1"/>
-      <c r="I344" s="1"/>
-      <c r="J344" s="1"/>
-      <c r="K344" s="1"/>
-      <c r="L344" s="1"/>
-      <c r="M344" s="1"/>
-      <c r="N344" s="1"/>
-      <c r="O344" s="1"/>
-      <c r="P344" s="1"/>
-      <c r="Q344" s="1"/>
-      <c r="R344" s="1"/>
-      <c r="S344" s="1"/>
-      <c r="T344" s="1"/>
-      <c r="U344" s="1"/>
-      <c r="V344" s="1"/>
-      <c r="W344" s="1"/>
-      <c r="X344" s="1"/>
-      <c r="Y344" s="1"/>
-      <c r="Z344" s="1"/>
-    </row>
-    <row r="345" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A345" s="1"/>
-      <c r="B345" s="1"/>
-      <c r="C345" s="1"/>
-      <c r="D345" s="1"/>
-      <c r="E345" s="1"/>
-      <c r="F345" s="1"/>
-      <c r="G345" s="1"/>
-      <c r="H345" s="1"/>
-      <c r="I345" s="1"/>
-      <c r="J345" s="1"/>
-      <c r="K345" s="1"/>
-      <c r="L345" s="1"/>
-      <c r="M345" s="1"/>
-      <c r="N345" s="1"/>
-      <c r="O345" s="1"/>
-      <c r="P345" s="1"/>
-      <c r="Q345" s="1"/>
-      <c r="R345" s="1"/>
-      <c r="S345" s="1"/>
-      <c r="T345" s="1"/>
-      <c r="U345" s="1"/>
-      <c r="V345" s="1"/>
-      <c r="W345" s="1"/>
-      <c r="X345" s="1"/>
-      <c r="Y345" s="1"/>
-      <c r="Z345" s="1"/>
-    </row>
-    <row r="346" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A346" s="1"/>
-      <c r="B346" s="1"/>
-      <c r="C346" s="1"/>
-      <c r="D346" s="1"/>
-      <c r="E346" s="1"/>
-      <c r="F346" s="1"/>
-      <c r="G346" s="1"/>
-      <c r="H346" s="1"/>
-      <c r="I346" s="1"/>
-      <c r="J346" s="1"/>
-      <c r="K346" s="1"/>
-      <c r="L346" s="1"/>
-      <c r="M346" s="1"/>
-      <c r="N346" s="1"/>
-      <c r="O346" s="1"/>
-      <c r="P346" s="1"/>
-      <c r="Q346" s="1"/>
-      <c r="R346" s="1"/>
-      <c r="S346" s="1"/>
-      <c r="T346" s="1"/>
-      <c r="U346" s="1"/>
-      <c r="V346" s="1"/>
-      <c r="W346" s="1"/>
-      <c r="X346" s="1"/>
-      <c r="Y346" s="1"/>
-      <c r="Z346" s="1"/>
-    </row>
-    <row r="347" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A347" s="1"/>
-      <c r="B347" s="1"/>
-      <c r="C347" s="1"/>
-      <c r="D347" s="1"/>
-      <c r="E347" s="1"/>
-      <c r="F347" s="1"/>
-      <c r="G347" s="1"/>
-      <c r="H347" s="1"/>
-      <c r="I347" s="1"/>
-      <c r="J347" s="1"/>
-      <c r="K347" s="1"/>
-      <c r="L347" s="1"/>
-      <c r="M347" s="1"/>
-      <c r="N347" s="1"/>
-      <c r="O347" s="1"/>
-      <c r="P347" s="1"/>
-      <c r="Q347" s="1"/>
-      <c r="R347" s="1"/>
-      <c r="S347" s="1"/>
-      <c r="T347" s="1"/>
-      <c r="U347" s="1"/>
-      <c r="V347" s="1"/>
-      <c r="W347" s="1"/>
-      <c r="X347" s="1"/>
-      <c r="Y347" s="1"/>
-      <c r="Z347" s="1"/>
-    </row>
   </sheetData>
-  <mergeCells count="72">
-    <mergeCell ref="A126:I126"/>
-    <mergeCell ref="A127:I127"/>
-    <mergeCell ref="A128:I128"/>
-    <mergeCell ref="A129:I129"/>
+  <mergeCells count="66">
+    <mergeCell ref="A118:I118"/>
+    <mergeCell ref="A119:I119"/>
+    <mergeCell ref="A120:I120"/>
     <mergeCell ref="A121:I121"/>
-    <mergeCell ref="A122:I122"/>
-    <mergeCell ref="A123:I123"/>
-    <mergeCell ref="A124:I124"/>
-    <mergeCell ref="A125:I125"/>
-    <mergeCell ref="B116:G116"/>
-    <mergeCell ref="B117:G117"/>
-    <mergeCell ref="B118:G118"/>
-    <mergeCell ref="B119:G119"/>
-    <mergeCell ref="B120:G120"/>
-    <mergeCell ref="B111:G111"/>
-    <mergeCell ref="B112:G112"/>
-    <mergeCell ref="B113:G113"/>
-    <mergeCell ref="B114:G114"/>
-    <mergeCell ref="B115:G115"/>
-    <mergeCell ref="A106:I106"/>
-    <mergeCell ref="B107:G107"/>
+    <mergeCell ref="A113:I113"/>
+    <mergeCell ref="A114:I114"/>
+    <mergeCell ref="A115:I115"/>
+    <mergeCell ref="A116:I116"/>
+    <mergeCell ref="A117:I117"/>
     <mergeCell ref="B108:G108"/>
     <mergeCell ref="B109:G109"/>
     <mergeCell ref="B110:G110"/>
+    <mergeCell ref="B111:G111"/>
+    <mergeCell ref="B112:G112"/>
+    <mergeCell ref="B103:G103"/>
+    <mergeCell ref="B104:G104"/>
+    <mergeCell ref="B105:G105"/>
+    <mergeCell ref="B106:G106"/>
+    <mergeCell ref="B107:G107"/>
+    <mergeCell ref="A98:I98"/>
+    <mergeCell ref="B99:G99"/>
+    <mergeCell ref="B100:G100"/>
+    <mergeCell ref="B101:G101"/>
+    <mergeCell ref="B102:G102"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="G89:I89"/>
+    <mergeCell ref="A90:I90"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="D91:E97"/>
+    <mergeCell ref="F91:I91"/>
+    <mergeCell ref="G92:I92"/>
+    <mergeCell ref="G93:I93"/>
+    <mergeCell ref="G94:I94"/>
+    <mergeCell ref="G95:I95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="G96:I96"/>
     <mergeCell ref="A97:C97"/>
-    <mergeCell ref="D97:F97"/>
     <mergeCell ref="G97:I97"/>
-    <mergeCell ref="A98:I98"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="D99:E105"/>
-    <mergeCell ref="F99:I99"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="G101:I101"/>
-    <mergeCell ref="G102:I102"/>
-    <mergeCell ref="G103:I103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="G104:I104"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="G105:I105"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="G76:I76"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="G55:I55"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="E19:E33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D33"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I33"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A13:B17"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:I17"/>
-    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="G68:I68"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="E11:E25"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="H24:I25"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="F25:G25"/>
     <mergeCell ref="A1:I2"/>
-    <mergeCell ref="A3:B11"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:I9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="14" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>